--- a/Outputs/Scenarios/PtX_demand_FI_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FI_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002049293468758665</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006625292838491123</v>
+        <v>0.007225934957707601</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01104215473081854</v>
+        <v>0.01040086215275063</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>2.952685001275128e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004416861892327416</v>
+        <v>0.004457512351178842</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003033729486396468</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03574437369586451</v>
+        <v>0.0389849212294041</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0595739561597742</v>
+        <v>0.05611409376310102</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001596699729682351</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02382958246390968</v>
+        <v>0.02404889732704329</v>
       </c>
     </row>
     <row r="43">
